--- a/data/availability/projects/pre-developments/stone-residence.xlsx
+++ b/data/availability/projects/pre-developments/stone-residence.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fact sheet inventory for stone-residence</t>
+          <t>Inventory for stone-residence</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,16 +564,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="F2" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="G2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -587,12 +587,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Ready to Move</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20% / 5 yrs</t>
+          <t>20% DP over 5 yrs</t>
         </is>
       </c>
     </row>
@@ -614,16 +614,16 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="F3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>12.31</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>12.31</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -637,12 +637,62 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Ready to Move</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20% / 5 yrs</t>
+          <t>20% DP over 5 yrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>stone-residence</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>220</v>
+      </c>
+      <c r="F4" t="n">
+        <v>220</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="H4" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Semi-finished</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ready to Move</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>20% DP over 5 yrs</t>
         </is>
       </c>
     </row>
@@ -657,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,7 +790,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SR-2BR</t>
+          <t>SR-2BR-140</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -757,7 +807,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
@@ -766,16 +816,16 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9380000</v>
+        <v>9702000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Ready to Move</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20% / 5 yrs</t>
+          <t>20% DP over 5 yrs</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -797,7 +847,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SR-3BR</t>
+          <t>SR-3BR-175</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -814,7 +864,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
@@ -823,19 +873,76 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12000000</v>
+        <v>12312000</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Ready to Move</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20% / 5 yrs</t>
+          <t>20% DP over 5 yrs</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>stone-residence</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SR-PH-220</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Semi-finished</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>220</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>15708000</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ready to Move</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>20% DP over 5 yrs</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Available</t>
         </is>

--- a/data/availability/projects/pre-developments/stone-residence.xlsx
+++ b/data/availability/projects/pre-developments/stone-residence.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for stone-residence</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -809,7 +819,6 @@
       <c r="G2" t="n">
         <v>140</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -866,7 +875,6 @@
       <c r="G3" t="n">
         <v>175</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -923,7 +931,6 @@
       <c r="G4" t="n">
         <v>220</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
